--- a/exam-scheduling-engine-main NSGA II/outputs/Ket_Qua_Xep_Lich.xlsx
+++ b/exam-scheduling-engine-main NSGA II/outputs/Ket_Qua_Xep_Lich.xlsx
@@ -18,10 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -60,12 +57,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,8 +488,10 @@
           <t>Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>46173</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -524,11 +522,11 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CB058, CB001</t>
+          <t>CB053, CB054, CB031, CB010</t>
         </is>
       </c>
     </row>
@@ -538,8 +536,10 @@
           <t>Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>46173</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -570,11 +570,11 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CB005</t>
+          <t>CB008, CB024, CB013, CB052</t>
         </is>
       </c>
     </row>
@@ -584,8 +584,10 @@
           <t>Thứ 2, 01/06/2026, Ca 1: 07g00-09g30</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>46174</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -616,11 +618,11 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CB001, CB027, CB047, CB049, CB019, CB015</t>
+          <t>CB026</t>
         </is>
       </c>
     </row>
@@ -630,8 +632,10 @@
           <t>Thứ 2, 01/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>46174</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -662,11 +666,11 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CB018, CB055, CB040, CB045, CB049, CB052</t>
+          <t>CB071, CB020, CB003, CB051, CB017, CB045, CB009, CB062, CB021, CB066, CB060, CB061, CB069, CB058, CB029, CB018, CB008, CB044, CB037, CB070, CB010, CB039, CB036, CB014, CB012, CB022, CB041, CB031, CB027, CB026, CB052, CB063</t>
         </is>
       </c>
     </row>
@@ -676,8 +680,10 @@
           <t>Thứ 2, 01/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>46174</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -708,11 +714,11 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CB041, CB021, CB013, CB044, CB036</t>
+          <t>CB032, CB012, CB046, CB059, CB013, CB036, CB016, CB047, CB020, CB001, CB010, CB069, CB030, CB052, CB068, CB054, CB058, CB019, CB048, CB065, CB027, CB035, CB007, CB002, CB021, CB066, CB037, CB045</t>
         </is>
       </c>
     </row>
@@ -722,8 +728,10 @@
           <t>Thứ 2, 01/06/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>46174</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -754,11 +762,11 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CB028, CB056, CB029, CB025, CB070, CB058, CB016</t>
+          <t>CB049</t>
         </is>
       </c>
     </row>
@@ -768,8 +776,10 @@
           <t>Thứ 2, 01/06/2026, Ca 5: 18g15-20g45</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>46174</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -800,11 +810,11 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CB061, CB054, CB053, CB026, CB063, CB030, CB069, CB038, CB004</t>
+          <t>CB024</t>
         </is>
       </c>
     </row>
@@ -814,8 +824,10 @@
           <t>Thứ 2, 08/06/2026, Ca 1: 07g00-09g30</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>46181</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:00:00</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -846,11 +858,11 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>CB011, CB050, CB026, CB055, CB008, CB044, CB028, CB012</t>
+          <t>CB016, CB049</t>
         </is>
       </c>
     </row>
@@ -860,8 +872,10 @@
           <t>Thứ 2, 08/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>46181</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:00:00</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -892,11 +906,11 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>CB003, CB068, CB059</t>
+          <t>CB013, CB056, CB006, CB053, CB001, CB007, CB059, CB068, CB017, CB063, CB055, CB022, CB011, CB035, CB009, CB014, CB034, CB025, CB015, CB031, CB021, CB040, CB062, CB033, CB004, CB036, CB069, CB027, CB067, CB061</t>
         </is>
       </c>
     </row>
@@ -906,8 +920,10 @@
           <t>Thứ 2, 08/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>46181</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:00:00</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -938,11 +954,11 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>CB006, CB065</t>
+          <t>CB051, CB023, CB046</t>
         </is>
       </c>
     </row>
@@ -952,8 +968,10 @@
           <t>Thứ 2, 08/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>46181</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:00:00</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -984,11 +1002,11 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>CB056, CB043, CB071, CB073, CB055, CB030, CB018, CB009, CB037</t>
+          <t>CB056, CB017, CB072, CB015, CB035, CB059, CB054, CB003, CB024, CB042, CB066, CB062, CB038, CB001, CB004, CB071, CB064, CB040, CB031, CB021, CB048, CB006, CB039, CB058, CB043, CB060, CB067, CB045, CB037, CB065</t>
         </is>
       </c>
     </row>
@@ -998,8 +1016,10 @@
           <t>Thứ 2, 08/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>46181</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:00:00</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1034,7 +1054,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CB061, CB027, CB053</t>
+          <t>CB052, CB049, CB050</t>
         </is>
       </c>
     </row>
@@ -1044,8 +1064,10 @@
           <t>Thứ 2, 08/06/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>46181</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:00:00</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1076,11 +1098,11 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>CB017, CB023, CB040, CB036, CB054, CB031</t>
+          <t>CB026, CB012, CB054, CB066</t>
         </is>
       </c>
     </row>
@@ -1090,8 +1112,10 @@
           <t>Thứ 2, 08/06/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>46181</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:00:00</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1122,11 +1146,11 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>CB042, CB021, CB005, CB001, CB029, CB004, CB045, CB008, CB072</t>
+          <t>CB049, CB018, CB070</t>
         </is>
       </c>
     </row>
@@ -1136,8 +1160,10 @@
           <t>Thứ 2, 18/05/2026, Ca 5: 18g15-20g45</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>46160</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-18 00:00:00</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1168,11 +1194,11 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>CB067, CB033, CB018, CB004, CB046</t>
+          <t>CB031, CB070</t>
         </is>
       </c>
     </row>
@@ -1182,8 +1208,10 @@
           <t>Thứ 2, 25/05/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>46167</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-25 00:00:00</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1214,11 +1242,11 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CB004, CB041, CB066, CB028, CB056, CB002, CB068, CB024, CB053</t>
+          <t>CB004, CB068, CB029, CB021, CB044, CB015, CB031, CB053, CB061, CB038, CB052, CB058, CB041, CB005, CB048, CB001, CB042</t>
         </is>
       </c>
     </row>
@@ -1228,8 +1256,10 @@
           <t>Thứ 2, 25/05/2026, Ca 5: 18g15-20g45</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
-        <v>46167</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-25 00:00:00</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1260,11 +1290,11 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>CB034, CB010, CB057, CB019, CB050, CB018</t>
+          <t>CB028, CB024, CB032</t>
         </is>
       </c>
     </row>
@@ -1274,8 +1304,10 @@
           <t>Thứ 3, 02/06/2026, Ca 1: 07g00-09g30</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>46175</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1306,11 +1338,11 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>CB024, CB039, CB019, CB017, CB052, CB033, CB060</t>
+          <t>CB057</t>
         </is>
       </c>
     </row>
@@ -1320,8 +1352,10 @@
           <t>Thứ 3, 02/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
-        <v>46175</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1352,11 +1386,11 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CB038, CB032, CB016</t>
+          <t>CB005, CB049, CB004, CB002, CB067, CB069, CB060, CB062, CB034, CB073, CB045, CB070, CB020, CB028, CB032, CB013, CB058, CB057, CB006, CB040, CB010, CB072, CB056, CB042, CB023, CB036, CB039, CB012, CB037, CB027, CB066, CB041</t>
         </is>
       </c>
     </row>
@@ -1366,8 +1400,10 @@
           <t>Thứ 3, 02/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>46175</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1398,11 +1434,11 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>CB006, CB037, CB010</t>
+          <t>CB031, CB020, CB059, CB041, CB054, CB058, CB021, CB009, CB050, CB002, CB039, CB029, CB037, CB018, CB045, CB057, CB026, CB005, CB053, CB073, CB055, CB030, CB052, CB048, CB038, CB071, CB047, CB008, CB068, CB007, CB070, CB042</t>
         </is>
       </c>
     </row>
@@ -1412,8 +1448,10 @@
           <t>Thứ 3, 02/06/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>46175</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1444,11 +1482,11 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>CB071, CB015, CB042, CB036, CB034, CB060, CB048</t>
+          <t>CB011, CB014, CB020, CB064, CB047, CB032, CB069, CB013, CB053, CB067, CB025, CB028, CB046, CB061, CB003</t>
         </is>
       </c>
     </row>
@@ -1458,8 +1496,10 @@
           <t>Thứ 3, 02/06/2026, Ca 5: 18g15-20g45</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
-        <v>46175</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1490,11 +1530,11 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>CB064, CB054, CB070</t>
+          <t>CB022, CB051</t>
         </is>
       </c>
     </row>
@@ -1504,8 +1544,10 @@
           <t>Thứ 3, 09/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
-        <v>46182</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-09 00:00:00</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1536,11 +1578,11 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>CB005, CB050, CB009</t>
+          <t>CB065, CB040, CB019, CB033, CB050</t>
         </is>
       </c>
     </row>
@@ -1550,8 +1592,10 @@
           <t>Thứ 3, 09/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>46182</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-09 00:00:00</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1582,11 +1626,11 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>CB012, CB040, CB029, CB015, CB057, CB061, CB006, CB064</t>
+          <t>CB034, CB020, CB032, CB004, CB028, CB038, CB066, CB012, CB030, CB002, CB023, CB042, CB039, CB007, CB018, CB022, CB036, CB006, CB052, CB051</t>
         </is>
       </c>
     </row>
@@ -1596,8 +1640,10 @@
           <t>Thứ 3, 09/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
-        <v>46182</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-09 00:00:00</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1628,11 +1674,11 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>CB017, CB065, CB035, CB044</t>
+          <t>CB005, CB064, CB053, CB041, CB018, CB059, CB010, CB008, CB006, CB022, CB034, CB027, CB073, CB062, CB029</t>
         </is>
       </c>
     </row>
@@ -1642,8 +1688,10 @@
           <t>Thứ 3, 09/06/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
-        <v>46182</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-09 00:00:00</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1674,11 +1722,11 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>CB034, CB051, CB013, CB043, CB001</t>
+          <t>CB035</t>
         </is>
       </c>
     </row>
@@ -1688,8 +1736,10 @@
           <t>Thứ 3, 19/05/2026, Ca 5: 18g15-20g45</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
-        <v>46161</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1720,11 +1770,11 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CB003, CB060, CB063, CB009, CB010</t>
+          <t>CB001, CB054, CB051</t>
         </is>
       </c>
     </row>
@@ -1734,8 +1784,10 @@
           <t>Thứ 3, 26/05/2026, Ca 5: 18g15-20g45</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
-        <v>46168</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-26 00:00:00</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1766,11 +1818,11 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>CB033, CB055, CB002</t>
+          <t>CB028, CB065</t>
         </is>
       </c>
     </row>
@@ -1780,8 +1832,10 @@
           <t>Thứ 4, 03/06/2026, Ca 1: 07g00-09g30</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
-        <v>46176</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-06-03 00:00:00</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1812,11 +1866,11 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>CB032, CB050, CB037, CB045, CB046, CB017, CB057, CB020, CB054</t>
+          <t>CB012, CB031, CB039, CB020, CB016, CB046, CB019, CB047, CB065, CB027, CB002, CB021, CB007, CB023, CB055, CB032, CB043, CB025, CB059, CB037, CB071, CB003, CB067, CB056, CB011, CB036, CB015, CB062, CB008, CB060, CB072</t>
         </is>
       </c>
     </row>
@@ -1826,8 +1880,10 @@
           <t>Thứ 4, 03/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
-        <v>46176</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-03 00:00:00</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1858,11 +1914,11 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>CB042, CB012, CB068, CB009, CB051</t>
+          <t>CB004, CB001, CB035, CB033, CB020, CB052, CB026, CB028, CB047, CB064, CB019, CB070, CB063, CB066, CB016, CB056, CB046, CB067, CB024, CB013, CB045, CB038, CB034, CB051, CB030, CB049, CB048, CB073, CB025, CB041, CB014</t>
         </is>
       </c>
     </row>
@@ -1872,8 +1928,10 @@
           <t>Thứ 4, 03/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
-        <v>46176</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-06-03 00:00:00</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1904,11 +1962,11 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>CB016, CB038, CB025, CB043, CB059, CB048, CB046</t>
+          <t>CB049, CB055, CB072, CB043, CB008, CB025, CB024, CB022, CB010, CB065, CB059, CB048, CB040, CB050, CB014, CB004, CB053, CB027, CB070, CB056, CB005, CB071, CB015, CB006, CB054, CB069, CB061, CB007, CB003, CB009, CB063</t>
         </is>
       </c>
     </row>
@@ -1918,8 +1976,10 @@
           <t>Thứ 4, 03/06/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
-        <v>46176</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-06-03 00:00:00</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1950,11 +2010,11 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>CB003</t>
+          <t>CB003, CB030, CB014, CB017, CB013, CB058, CB036, CB012, CB050, CB051, CB069, CB032, CB020, CB066, CB047, CB043, CB037, CB048, CB065, CB045, CB073</t>
         </is>
       </c>
     </row>
@@ -1964,8 +2024,10 @@
           <t>Thứ 4, 10/06/2026, Ca 1: 07g00-09g30</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
-        <v>46183</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1996,11 +2058,11 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>CB043, CB066, CB038</t>
+          <t>CB005</t>
         </is>
       </c>
     </row>
@@ -2010,8 +2072,10 @@
           <t>Thứ 4, 10/06/2026, Ca 1: 07g00-09g30</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n">
-        <v>46183</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2042,11 +2106,11 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>CB003, CB031, CB018, CB047, CB021, CB061</t>
+          <t>CB002</t>
         </is>
       </c>
     </row>
@@ -2056,8 +2120,10 @@
           <t>Thứ 4, 10/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
-        <v>46183</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2088,11 +2154,11 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>CB009, CB005</t>
+          <t>CB036</t>
         </is>
       </c>
     </row>
@@ -2102,8 +2168,10 @@
           <t>Thứ 4, 10/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
-        <v>46183</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2138,7 +2206,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>CB051, CB041, CB067, CB027, CB064</t>
+          <t>CB016, CB057, CB058, CB011, CB032</t>
         </is>
       </c>
     </row>
@@ -2148,8 +2216,10 @@
           <t>Thứ 4, 10/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
-        <v>46183</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2180,11 +2250,11 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>CB053</t>
+          <t>CB003, CB043, CB013, CB044, CB030, CB052, CB073, CB039, CB010, CB072, CB045, CB033, CB022, CB002, CB004, CB049, CB012, CB071, CB064, CB060, CB023, CB017, CB009, CB068, CB034, CB040, CB005, CB046, CB051, CB029</t>
         </is>
       </c>
     </row>
@@ -2194,8 +2264,10 @@
           <t>Thứ 4, 10/06/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
-        <v>46183</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-10 00:00:00</t>
+        </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2226,11 +2298,11 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>CB060, CB049</t>
+          <t>CB056</t>
         </is>
       </c>
     </row>
@@ -2240,8 +2312,10 @@
           <t>Thứ 4, 27/05/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
-        <v>46169</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2272,11 +2346,11 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>CB056, CB013, CB008, CB006</t>
+          <t>CB044, CB009</t>
         </is>
       </c>
     </row>
@@ -2286,8 +2360,10 @@
           <t>Thứ 4, 27/05/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n">
-        <v>46169</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2322,7 +2398,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>CB030</t>
+          <t>CB073</t>
         </is>
       </c>
     </row>
@@ -2332,8 +2408,10 @@
           <t>Thứ 4, 27/05/2026, Ca 5: 18g15-20g45</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
-        <v>46169</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2364,11 +2442,11 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>CB034</t>
+          <t>CB019, CB041, CB030, CB054</t>
         </is>
       </c>
     </row>
@@ -2378,8 +2456,10 @@
           <t>Thứ 5, 04/06/2026, Ca 1: 07g00-09g30</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
-        <v>46177</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:00:00</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2410,11 +2490,11 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>CB035</t>
+          <t>CB011, CB034, CB004, CB046, CB016, CB040, CB066, CB055, CB047, CB038</t>
         </is>
       </c>
     </row>
@@ -2424,8 +2504,10 @@
           <t>Thứ 5, 04/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
-        <v>46177</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:00:00</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2456,11 +2538,11 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>CB027, CB052, CB058, CB069</t>
+          <t>CB065, CB043, CB063, CB010, CB009, CB035, CB015</t>
         </is>
       </c>
     </row>
@@ -2470,8 +2552,10 @@
           <t>Thứ 5, 04/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
-        <v>46177</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:00:00</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2502,11 +2586,11 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>CB012, CB070, CB047, CB041, CB022, CB023, CB062</t>
+          <t>CB044, CB066, CB029, CB048</t>
         </is>
       </c>
     </row>
@@ -2516,8 +2600,10 @@
           <t>Thứ 5, 04/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n">
-        <v>46177</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:00:00</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2548,11 +2634,11 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>CB032</t>
+          <t>CB051, CB053</t>
         </is>
       </c>
     </row>
@@ -2562,8 +2648,10 @@
           <t>Thứ 5, 11/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
-        <v>46184</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2594,11 +2682,11 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>CB052, CB036, CB062, CB071</t>
+          <t>CB055, CB008</t>
         </is>
       </c>
     </row>
@@ -2608,8 +2696,10 @@
           <t>Thứ 5, 11/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n">
-        <v>46184</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2640,11 +2730,11 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>CB023, CB024, CB066, CB014, CB015</t>
+          <t>CB051, CB002, CB072, CB030, CB021, CB045, CB039, CB003, CB042, CB022, CB037, CB070, CB065, CB041, CB009, CB012, CB046, CB015, CB007, CB050, CB018, CB016, CB057, CB043, CB001, CB035, CB027, CB058, CB011</t>
         </is>
       </c>
     </row>
@@ -2654,8 +2744,10 @@
           <t>Thứ 5, 11/06/2026, Ca1 : 07g00-09g30</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n">
-        <v>46184</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:00:00</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2686,11 +2778,11 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>CB029, CB065, CB048, CB020, CB062, CB049, CB013, CB002, CB054</t>
+          <t>CB063</t>
         </is>
       </c>
     </row>
@@ -2700,8 +2792,10 @@
           <t>Thứ 5, 21/05/2026, Ca 5: 18g15-20g45</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n">
-        <v>46163</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:00:00</t>
+        </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2732,11 +2826,11 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>CB053, CB014, CB022, CB048, CB010, CB039, CB072, CB007, CB032</t>
+          <t>CB023, CB010</t>
         </is>
       </c>
     </row>
@@ -2746,8 +2840,10 @@
           <t>Thứ 5, 28/05/2026, Ca 1: 07g00-09g30</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n">
-        <v>46170</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2778,11 +2874,11 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>CB057, CB051, CB053, CB070, CB036</t>
+          <t>CB036</t>
         </is>
       </c>
     </row>
@@ -2792,8 +2888,10 @@
           <t>Thứ 5, 28/05/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
-        <v>46170</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2824,11 +2922,11 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>CB012, CB017, CB046</t>
+          <t>CB063</t>
         </is>
       </c>
     </row>
@@ -2838,8 +2936,10 @@
           <t>Thứ 5, 28/05/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n">
-        <v>46170</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2874,7 +2974,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>CB031</t>
+          <t>CB056</t>
         </is>
       </c>
     </row>
@@ -2884,8 +2984,10 @@
           <t>Thứ 5, 28/05/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n">
-        <v>46170</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2916,11 +3018,11 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>CB025, CB056, CB007, CB067, CB011, CB001, CB010, CB065, CB023</t>
+          <t>CB050, CB029, CB042, CB037, CB035, CB047, CB058, CB053, CB006, CB034, CB044, CB049, CB033, CB026</t>
         </is>
       </c>
     </row>
@@ -2930,8 +3032,10 @@
           <t>Thứ 5, 28/05/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n">
-        <v>46170</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2962,11 +3066,11 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>CB063, CB049, CB042, CB033, CB026, CB013, CB039</t>
+          <t>CB064</t>
         </is>
       </c>
     </row>
@@ -2976,8 +3080,10 @@
           <t>Thứ 5, 28/05/2026, Ca 5: 18g15-20g45</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n">
-        <v>46170</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3008,11 +3114,11 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>CB002, CB073</t>
+          <t>CB038, CB021, CB054</t>
         </is>
       </c>
     </row>
@@ -3022,8 +3128,10 @@
           <t>Thứ 6, 05/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n">
-        <v>46178</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:00:00</t>
+        </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3054,11 +3162,11 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>CB051, CB019, CB073, CB072, CB065, CB040, CB048, CB059</t>
+          <t>CB057, CB068, CB019, CB032, CB035, CB039, CB022, CB048, CB001, CB028, CB044, CB054, CB015, CB002, CB070, CB042, CB059, CB050, CB060, CB014, CB067, CB011</t>
         </is>
       </c>
     </row>
@@ -3068,8 +3176,10 @@
           <t>Thứ 6, 05/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n">
-        <v>46178</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:00:00</t>
+        </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3100,11 +3210,11 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>CB064, CB063, CB004, CB020, CB016, CB058, CB047, CB036</t>
+          <t>CB068, CB023, CB034, CB050, CB030, CB060, CB031, CB047, CB020, CB033, CB018, CB025, CB006, CB003, CB062, CB065, CB063, CB069, CB016, CB026, CB043, CB029, CB008, CB072, CB071, CB038, CB064, CB057, CB061, CB052</t>
         </is>
       </c>
     </row>
@@ -3114,8 +3224,10 @@
           <t>Thứ 6, 05/06/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n">
-        <v>46178</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:00:00</t>
+        </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3146,11 +3258,11 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>CB029, CB050, CB027, CB069, CB071, CB011, CB022</t>
+          <t>CB027, CB007, CB023, CB004, CB008</t>
         </is>
       </c>
     </row>
@@ -3160,8 +3272,10 @@
           <t>Thứ 6, 12/06/2026, Ca 1: 07g00-09g30</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n">
-        <v>46185</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3192,11 +3306,11 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>CB024, CB018</t>
+          <t>CB046, CB001, CB044, CB067, CB042, CB060, CB061, CB009, CB043, CB019, CB028, CB032, CB002, CB026, CB050, CB058, CB017, CB064, CB030, CB011, CB022, CB031, CB012, CB014, CB033, CB021, CB029, CB073, CB025, CB057, CB015, CB072</t>
         </is>
       </c>
     </row>
@@ -3206,8 +3320,10 @@
           <t>Thứ 6, 12/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n">
-        <v>46185</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3238,11 +3354,11 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>CB040, CB007, CB028, CB020, CB034, CB022, CB014, CB037</t>
+          <t>CB019, CB002, CB061, CB062, CB071, CB034</t>
         </is>
       </c>
     </row>
@@ -3252,8 +3368,10 @@
           <t>Thứ 6, 12/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n">
-        <v>46185</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3284,11 +3402,11 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>CB050, CB045, CB021, CB071</t>
+          <t>CB017, CB011, CB031, CB006, CB047, CB016, CB014, CB019, CB013, CB050, CB057, CB018, CB024, CB055, CB049, CB056, CB069, CB005, CB026, CB033, CB009, CB036, CB028, CB007, CB008, CB022, CB040, CB060, CB041, CB035, CB012</t>
         </is>
       </c>
     </row>
@@ -3298,8 +3416,10 @@
           <t>Thứ 6, 12/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n">
-        <v>46185</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3330,11 +3450,11 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>CB016</t>
+          <t>CB029, CB023</t>
         </is>
       </c>
     </row>
@@ -3344,8 +3464,10 @@
           <t>Thứ 6, 12/06/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n">
-        <v>46185</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3376,11 +3498,11 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>CB051, CB015, CB062</t>
+          <t>CB053, CB045, CB044, CB061, CB063, CB033, CB068, CB010, CB071, CB055, CB060, CB049, CB017, CB035, CB026, CB056, CB025, CB054, CB066, CB072, CB027</t>
         </is>
       </c>
     </row>
@@ -3390,8 +3512,10 @@
           <t>Thứ 6, 12/06/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
-        <v>46185</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:00:00</t>
+        </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3422,11 +3546,11 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>CB025, CB055, CB041, CB035, CB019, CB061, CB026</t>
+          <t>CB034</t>
         </is>
       </c>
     </row>
@@ -3436,8 +3560,10 @@
           <t>Thứ 6, 22/05/2026, Ca 5: 18g15-20g45</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
-        <v>46164</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-05-22 00:00:00</t>
+        </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3468,11 +3594,11 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>CB046, CB009, CB039</t>
+          <t>CB024, CB025</t>
         </is>
       </c>
     </row>
@@ -3482,8 +3608,10 @@
           <t>Thứ 6, 29/05/2026, Ca 1: 07g00-09g30</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n">
-        <v>46171</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-05-29 00:00:00</t>
+        </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3514,11 +3642,11 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>CB049, CB038, CB064, CB031, CB072, CB052</t>
+          <t>CB013</t>
         </is>
       </c>
     </row>
@@ -3528,8 +3656,10 @@
           <t>Thứ 6, 29/05/2026, Ca 1: 07g00-09g30</t>
         </is>
       </c>
-      <c r="B68" s="2" t="n">
-        <v>46171</v>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-05-29 00:00:00</t>
+        </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3560,11 +3690,11 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>CB024, CB073, CB012, CB011, CB025, CB020, CB008</t>
+          <t>CB069, CB071, CB001, CB062, CB061, CB018, CB073, CB040, CB067, CB032, CB045, CB039, CB028, CB005, CB038, CB047, CB017, CB063, CB015, CB059, CB036, CB068, CB007, CB006, CB011, CB016, CB003, CB014, CB070, CB064, CB009</t>
         </is>
       </c>
     </row>
@@ -3574,8 +3704,10 @@
           <t>Thứ 6, 29/05/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n">
-        <v>46171</v>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-05-29 00:00:00</t>
+        </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3606,11 +3738,11 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>CB043, CB067, CB016, CB068, CB069, CB007, CB015</t>
+          <t>CB044</t>
         </is>
       </c>
     </row>
@@ -3620,8 +3752,10 @@
           <t>Thứ 6, 29/05/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n">
-        <v>46171</v>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-05-29 00:00:00</t>
+        </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3652,11 +3786,11 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>CB032, CB023, CB062, CB033, CB021</t>
+          <t>CB001</t>
         </is>
       </c>
     </row>
@@ -3666,8 +3800,10 @@
           <t>Thứ 6, 29/05/2026, Ca 5: 18g15-20g45</t>
         </is>
       </c>
-      <c r="B71" s="2" t="n">
-        <v>46171</v>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-05-29 00:00:00</t>
+        </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3698,11 +3834,11 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>CB005</t>
+          <t>CB023, CB041, CB037</t>
         </is>
       </c>
     </row>
@@ -3712,8 +3848,10 @@
           <t>Thứ 7, 13/06/2026, Ca 1: 07g00-09g30</t>
         </is>
       </c>
-      <c r="B72" s="2" t="n">
-        <v>46186</v>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3748,7 +3886,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>CB068, CB006, CB022, CB008</t>
+          <t>CB043, CB015, CB024, CB072</t>
         </is>
       </c>
     </row>
@@ -3758,8 +3896,10 @@
           <t>Thứ 7, 13/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n">
-        <v>46186</v>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3790,11 +3930,11 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>CB047</t>
+          <t>CB044, CB024</t>
         </is>
       </c>
     </row>
@@ -3804,8 +3944,10 @@
           <t>Thứ 7, 13/06/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n">
-        <v>46186</v>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3836,11 +3978,11 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>CB028, CB035, CB042, CB048, CB003, CB031, CB067, CB037</t>
+          <t>CB019, CB042, CB040, CB053, CB016, CB017</t>
         </is>
       </c>
     </row>
@@ -3850,8 +3992,10 @@
           <t>Thứ 7, 13/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n">
-        <v>46186</v>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3882,11 +4026,11 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>CB045, CB066, CB014, CB055, CB046, CB058</t>
+          <t>CB018, CB041, CB057, CB063</t>
         </is>
       </c>
     </row>
@@ -3896,8 +4040,10 @@
           <t>Thứ 7, 13/06/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n">
-        <v>46186</v>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3928,11 +4074,11 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>CB030, CB007, CB004, CB062, CB063, CB052, CB059, CB013, CB060</t>
+          <t>CB021, CB030, CB055, CB059, CB046, CB064</t>
         </is>
       </c>
     </row>
@@ -3942,8 +4088,10 @@
           <t>Thứ 7, 13/06/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n">
-        <v>46186</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3974,11 +4122,11 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>CB024</t>
+          <t>CB013, CB033, CB008, CB073</t>
         </is>
       </c>
     </row>
@@ -3988,8 +4136,10 @@
           <t>Thứ 7, 13/06/2026, Ca 4: 15g30-18g00</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n">
-        <v>46186</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-06-13 00:00:00</t>
+        </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4020,11 +4170,11 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>CB070</t>
+          <t>CB055, CB064, CB048, CB062, CB005, CB011</t>
         </is>
       </c>
     </row>
@@ -4034,8 +4184,10 @@
           <t>Thứ 7, 23/05/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n">
-        <v>46165</v>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4066,11 +4218,11 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>CB066, CB044, CB039, CB057</t>
+          <t>CB068, CB046, CB007, CB017, CB051, CB065</t>
         </is>
       </c>
     </row>
@@ -4080,8 +4232,10 @@
           <t>Thứ 7, 30/05/2026, Ca 2: 09g30-12g00</t>
         </is>
       </c>
-      <c r="B80" s="2" t="n">
-        <v>46172</v>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4112,11 +4266,11 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>CB011, CB035, CB030, CB072, CB059, CB047</t>
+          <t>CB006, CB025, CB033, CB038</t>
         </is>
       </c>
     </row>
@@ -4126,8 +4280,10 @@
           <t>Thứ 7, 30/05/2026, Ca 3: 13g00-15g30</t>
         </is>
       </c>
-      <c r="B81" s="2" t="n">
-        <v>46172</v>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4158,11 +4314,11 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>CB069, CB002, CB003, CB073, CB014, CB001, CB044, CB026, CB057</t>
+          <t>CB004, CB003, CB056, CB067</t>
         </is>
       </c>
     </row>
@@ -4248,11 +4404,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2); 20260530_3 (Cơ sở 1); 20260531_2 (Cơ sở 1); 20260601_1 (Cơ sở 2); 20260608_4 (Cơ sở 2); 20260609_4 (Cơ sở 2)</t>
+          <t>20260519_5 (Cơ sở 1); 20260525_2 (Cơ sở 2); 20260529_1 (Cơ sở 2); 20260529_3 (Cơ sở 1); 20260601_3 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4282,11 +4438,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2); 20260526_5 (Cơ sở 1); 20260528_5 (Cơ sở 1); 20260530_3 (Cơ sở 1); 20260611_1 (Cơ sở 1)</t>
+          <t>20260601_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_2 (Cơ sở 1); 20260610_1 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4316,11 +4472,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>20260519_5 (Cơ sở 1); 20260530_3 (Cơ sở 1); 20260603_4 (Cơ sở 2); 20260608_2 (Cơ sở 1); 20260613_2 (Cơ sở 2); 20260610_1 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2); 20260530_3 (Cơ sở 1); 20260601_2 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260611_3 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4350,11 +4506,11 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1); 20260525_2 (Cơ sở 2); 20260601_5 (Cơ sở 1); 20260605_3 (Cơ sở 1); 20260613_3 (Cơ sở 2); 20260608_4 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2); 20260530_3 (Cơ sở 1); 20260602_2 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260604_1 (Cơ sở 2); 20260605_4 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260610_3 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4384,11 +4540,11 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>20260529_5 (Cơ sở 1); 20260531_3 (Cơ sở 1); 20260609_2 (Cơ sở 1); 20260608_4 (Cơ sở 2); 20260610_2 (Cơ sở 1)</t>
+          <t>20260525_2 (Cơ sở 2); 20260529_1 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260609_3 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260612_3 (Cơ sở 1); 20260613_4 (Cơ sở 2); 20260610_1 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4418,11 +4574,11 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20260527_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260609_2 (Cơ sở 2); 20260613_1 (Cơ sở 1); 20260608_2 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2); 20260529_1 (Cơ sở 2); 20260530_2 (Cơ sở 1); 20260602_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260609_3 (Cơ sở 2); 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4452,11 +4608,11 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1); 20260528_3 (Cơ sở 2); 20260529_2 (Cơ sở 1); 20260612_2 (Cơ sở 1); 20260613_3 (Cơ sở 2)</t>
+          <t>20260523_3 (Cơ sở 1); 20260529_1 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260605_4 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4486,11 +4642,11 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20260527_2 (Cơ sở 2); 20260529_1 (Cơ sở 2); 20260613_1 (Cơ sở 1); 20260608_1 (Cơ sở 2); 20260608_4 (Cơ sở 2)</t>
+          <t>20260531_3 (Cơ sở 1); 20260601_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260605_4 (Cơ sở 1); 20260609_3 (Cơ sở 2); 20260611_3 (Cơ sở 1); 20260612_3 (Cơ sở 1); 20260613_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4520,11 +4676,11 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>20260519_5 (Cơ sở 1); 20260522_5 (Cơ sở 1); 20260603_2 (Cơ sở 2); 20260608_3 (Cơ sở 1); 20260609_2 (Cơ sở 1); 20260610_2 (Cơ sở 1)</t>
+          <t>20260527_2 (Cơ sở 2); 20260529_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260604_2 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4554,11 +4710,11 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20260519_5 (Cơ sở 1); 20260521_5 (Cơ sở 1); 20260525_5 (Cơ sở 1); 20260528_3 (Cơ sở 2); 20260602_3 (Cơ sở 2)</t>
+          <t>20260521_5 (Cơ sở 1); 20260531_2 (Cơ sở 1); 20260601_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260604_2 (Cơ sở 1); 20260609_3 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260612_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4588,11 +4744,11 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2); 20260529_1 (Cơ sở 2); 20260530_2 (Cơ sở 1); 20260605_4 (Cơ sở 1); 20260608_1 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260604_1 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260610_3 (Cơ sở 1); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 1); 20260613_4 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4622,11 +4778,11 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>20260528_2 (Cơ sở 1); 20260529_1 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260604_2 (Cơ sở 2); 20260609_2 (Cơ sở 2); 20260608_1 (Cơ sở 2)</t>
+          <t>20260601_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260608_4 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4656,11 +4812,11 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>20260527_2 (Cơ sở 2); 20260528_4 (Cơ sở 1); 20260601_3 (Cơ sở 2); 20260613_3 (Cơ sở 2); 20260609_4 (Cơ sở 2); 20260611_1 (Cơ sở 1)</t>
+          <t>20260529_1 (Cơ sở 1); 20260531_3 (Cơ sở 1); 20260601_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260608_2 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260612_3 (Cơ sở 1); 20260613_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4690,11 +4846,11 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1); 20260530_3 (Cơ sở 1); 20260611_3 (Cơ sở 2); 20260612_2 (Cơ sở 1); 20260613_3 (Cơ sở 1)</t>
+          <t>20260529_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4724,11 +4880,11 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>20260529_2 (Cơ sở 1); 20260601_1 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260609_2 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_4 (Cơ sở 1)</t>
+          <t>20260525_2 (Cơ sở 2); 20260529_1 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260604_2 (Cơ sở 1); 20260605_2 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260613_1 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4758,11 +4914,11 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>20260529_2 (Cơ sở 1); 20260601_4 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260612_3 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260604_1 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260610_3 (Cơ sở 1); 20260611_3 (Cơ sở 2); 20260612_3 (Cơ sở 1); 20260613_2 (Cơ sở 2); 20260608_1 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4792,11 +4948,11 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>20260528_2 (Cơ sở 1); 20260602_1 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260608_4 (Cơ sở 1); 20260609_3 (Cơ sở 2)</t>
+          <t>20260523_3 (Cơ sở 1); 20260529_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260608_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 1); 20260612_4 (Cơ sở 1); 20260613_2 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4826,11 +4982,11 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1); 20260525_5 (Cơ sở 1); 20260601_2 (Cơ sở 2); 20260608_3 (Cơ sở 1); 20260612_1 (Cơ sở 1); 20260610_1 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260609_3 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_3 (Cơ sở 1); 20260613_3 (Cơ sở 1); 20260608_4 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4860,11 +5016,11 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>20260525_5 (Cơ sở 1); 20260601_1 (Cơ sở 2); 20260602_1 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260612_4 (Cơ sở 2)</t>
+          <t>20260527_5 (Cơ sở 1); 20260601_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260609_2 (Cơ sở 1); 20260612_1 (Cơ sở 1); 20260612_2 (Cơ sở 1); 20260612_3 (Cơ sở 1); 20260613_2 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4894,11 +5050,11 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260612_2 (Cơ sở 1); 20260611_1 (Cơ sở 1)</t>
+          <t>20260601_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260609_2 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4928,11 +5084,11 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>20260529_3 (Cơ sở 1); 20260601_3 (Cơ sở 2); 20260612_3 (Cơ sở 1); 20260608_4 (Cơ sở 2); 20260610_1 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2); 20260528_5 (Cơ sở 1); 20260601_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260608_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260613_3 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4962,11 +5118,11 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1); 20260604_2 (Cơ sở 2); 20260605_4 (Cơ sở 1); 20260612_2 (Cơ sở 1); 20260613_1 (Cơ sở 1)</t>
+          <t>20260601_2 (Cơ sở 2); 20260602_5 (Cơ sở 1); 20260603_3 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260609_3 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4996,11 +5152,11 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2); 20260529_3 (Cơ sở 1); 20260604_2 (Cơ sở 2); 20260608_4 (Cơ sở 1); 20260611_3 (Cơ sở 2)</t>
+          <t>20260521_5 (Cơ sở 1); 20260529_5 (Cơ sở 1); 20260602_2 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260605_4 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260608_2 (Cơ sở 2); 20260612_3 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5030,11 +5186,11 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2); 20260529_1 (Cơ sở 2); 20260602_1 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260613_4 (Cơ sở 1)</t>
+          <t>20260522_5 (Cơ sở 1); 20260525_5 (Cơ sở 1); 20260531_3 (Cơ sở 1); 20260601_5 (Cơ sở 1); 20260603_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260608_3 (Cơ sở 1); 20260612_3 (Cơ sở 1); 20260613_1 (Cơ sở 1); 20260613_2 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5064,11 +5220,11 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2); 20260529_1 (Cơ sở 2); 20260601_4 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260612_4 (Cơ sở 2)</t>
+          <t>20260522_5 (Cơ sở 1); 20260530_2 (Cơ sở 1); 20260602_4 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260612_1 (Cơ sở 1); 20260612_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5098,11 +5254,11 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>20260528_4 (Cơ sở 1); 20260530_3 (Cơ sở 1); 20260601_5 (Cơ sở 1); 20260608_1 (Cơ sở 2); 20260612_4 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2); 20260601_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_4 (Cơ sở 1); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 1); 20260612_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5132,11 +5288,11 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>20260601_1 (Cơ sở 2); 20260604_2 (Cơ sở 1); 20260605_4 (Cơ sở 1); 20260610_3 (Cơ sở 1); 20260608_3 (Cơ sở 2)</t>
+          <t>20260601_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260605_4 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260609_3 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5166,11 +5322,11 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2); 20260601_4 (Cơ sở 2); 20260612_2 (Cơ sở 1); 20260613_2 (Cơ sở 2); 20260608_1 (Cơ sở 2)</t>
+          <t>20260525_5 (Cơ sở 1); 20260526_5 (Cơ sở 1); 20260529_1 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5200,11 +5356,11 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>20260601_4 (Cơ sở 2); 20260605_4 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260608_4 (Cơ sở 2); 20260611_1 (Cơ sở 1)</t>
+          <t>20260525_2 (Cơ sở 2); 20260528_3 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260604_2 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260609_3 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5234,11 +5390,11 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>20260527_4 (Cơ sở 1); 20260530_2 (Cơ sở 1); 20260601_5 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260613_3 (Cơ sở 2)</t>
+          <t>20260527_5 (Cơ sở 1); 20260601_3 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260613_3 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5268,11 +5424,11 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 1); 20260529_1 (Cơ sở 1); 20260608_4 (Cơ sở 1); 20260613_2 (Cơ sở 2); 20260610_1 (Cơ sở 2)</t>
+          <t>20260518_5 (Cơ sở 1); 20260525_2 (Cơ sở 2); 20260531_2 (Cơ sở 1); 20260601_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5302,11 +5458,11 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1); 20260529_3 (Cơ sở 1); 20260602_2 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260604_3 (Cơ sở 2)</t>
+          <t>20260525_5 (Cơ sở 1); 20260529_1 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260610_3 (Cơ sở 1); 20260612_1 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5336,11 +5492,11 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1); 20260526_5 (Cơ sở 1); 20260528_4 (Cơ sở 1); 20260529_3 (Cơ sở 1); 20260602_1 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2); 20260530_2 (Cơ sở 1); 20260603_2 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260609_2 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 1); 20260612_4 (Cơ sở 1); 20260613_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5370,11 +5526,11 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>20260525_5 (Cơ sở 1); 20260527_5 (Cơ sở 1); 20260602_4 (Cơ sở 2); 20260612_2 (Cơ sở 1); 20260609_4 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260604_1 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260609_3 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260612_2 (Cơ sở 1); 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5404,11 +5560,11 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>20260530_2 (Cơ sở 1); 20260604_1 (Cơ sở 2); 20260609_3 (Cơ sở 2); 20260613_2 (Cơ sở 2); 20260612_4 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260604_2 (Cơ sở 1); 20260605_2 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260611_3 (Cơ sở 2); 20260612_3 (Cơ sở 1); 20260612_4 (Cơ sở 1); 20260609_4 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5438,11 +5594,11 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>20260528_1 (Cơ sở 1); 20260601_3 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_4 (Cơ sở 1); 20260611_3 (Cơ sở 1)</t>
+          <t>20260528_1 (Cơ sở 1); 20260529_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260608_2 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260612_3 (Cơ sở 1); 20260610_2 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5472,11 +5628,11 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>20260602_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260608_3 (Cơ sở 1); 20260612_2 (Cơ sở 1); 20260613_2 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2); 20260529_5 (Cơ sở 1); 20260601_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260608_3 (Cơ sở 1); 20260611_3 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5506,11 +5662,11 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 1); 20260601_5 (Cơ sở 1); 20260602_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260610_1 (Cơ sở 1)</t>
+          <t>20260525_2 (Cơ sở 2); 20260528_5 (Cơ sở 1); 20260529_1 (Cơ sở 2); 20260530_2 (Cơ sở 1); 20260602_3 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260604_1 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260609_2 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5540,11 +5696,11 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1); 20260522_5 (Cơ sở 1); 20260523_3 (Cơ sở 1); 20260528_4 (Cơ sở 1); 20260602_1 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260611_3 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5574,11 +5730,11 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>20260601_2 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260608_4 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260612_2 (Cơ sở 1)</t>
+          <t>20260529_1 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260604_1 (Cơ sở 2); 20260608_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260609_2 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260612_3 (Cơ sở 1); 20260613_2 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5608,11 +5764,11 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260604_2 (Cơ sở 2); 20260610_3 (Cơ sở 1); 20260612_4 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2); 20260527_5 (Cơ sở 1); 20260529_5 (Cơ sở 1); 20260601_2 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260609_3 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_3 (Cơ sở 1); 20260613_3 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5642,11 +5798,11 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>20260528_4 (Cơ sở 1); 20260602_4 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260613_2 (Cơ sở 2); 20260608_4 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2); 20260528_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260613_2 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5676,11 +5832,11 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>20260529_2 (Cơ sở 1); 20260603_3 (Cơ sở 2); 20260608_3 (Cơ sở 1); 20260609_4 (Cơ sở 2); 20260610_1 (Cơ sở 1)</t>
+          <t>20260603_1 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260604_2 (Cơ sở 1); 20260605_3 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260613_1 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5710,11 +5866,11 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>20260523_3 (Cơ sở 1); 20260530_3 (Cơ sở 1); 20260601_3 (Cơ sở 2); 20260609_3 (Cơ sở 2); 20260608_1 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2); 20260527_2 (Cơ sở 2); 20260528_3 (Cơ sở 2); 20260529_2 (Cơ sở 1); 20260601_2 (Cơ sở 2); 20260604_2 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_4 (Cơ sở 1); 20260613_2 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5744,11 +5900,11 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>20260601_2 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260612_3 (Cơ sở 1); 20260613_3 (Cơ sở 1); 20260608_4 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260608_3 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5778,11 +5934,11 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1); 20260522_5 (Cơ sở 1); 20260528_2 (Cơ sở 1); 20260603_1 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260613_3 (Cơ sở 1)</t>
+          <t>20260523_3 (Cơ sở 1); 20260601_3 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260604_1 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260613_3 (Cơ sở 2); 20260608_2 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5812,11 +5968,11 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>20260530_2 (Cơ sở 1); 20260601_1 (Cơ sở 2); 20260604_2 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260613_2 (Cơ sở 1); 20260610_1 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2); 20260529_1 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260604_1 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5846,11 +6002,11 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1); 20260602_4 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260613_2 (Cơ sở 2); 20260611_1 (Cơ sở 1)</t>
+          <t>20260525_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260604_2 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260613_4 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5880,11 +6036,11 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>20260528_4 (Cơ sở 1); 20260529_1 (Cơ sở 1); 20260601_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260610_4 (Cơ sở 1); 20260611_1 (Cơ sở 1)</t>
+          <t>20260528_3 (Cơ sở 2); 20260601_4 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260612_3 (Cơ sở 1); 20260612_4 (Cơ sở 1); 20260608_1 (Cơ sở 2); 20260608_3 (Cơ sở 2); 20260608_4 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5914,11 +6070,11 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>20260525_5 (Cơ sở 1); 20260603_1 (Cơ sở 2); 20260605_4 (Cơ sở 1); 20260609_2 (Cơ sở 1); 20260612_3 (Cơ sở 1); 20260608_1 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260605_3 (Cơ sở 1); 20260609_2 (Cơ sở 1); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 1); 20260608_3 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5948,11 +6104,11 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>20260528_1 (Cơ sở 1); 20260603_2 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260610_3 (Cơ sở 1); 20260612_4 (Cơ sở 1); 20260609_4 (Cơ sở 2)</t>
+          <t>20260519_5 (Cơ sở 1); 20260523_3 (Cơ sở 1); 20260601_2 (Cơ sở 2); 20260602_5 (Cơ sở 1); 20260603_2 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260604_3 (Cơ sở 2); 20260609_2 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260608_2 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5982,11 +6138,11 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 1); 20260601_2 (Cơ sở 2); 20260602_1 (Cơ sở 2); 20260604_2 (Cơ sở 1); 20260611_3 (Cơ sở 1); 20260613_3 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2); 20260531_3 (Cơ sở 1); 20260601_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260608_3 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -6016,11 +6172,11 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1); 20260525_2 (Cơ sở 2); 20260528_1 (Cơ sở 1); 20260601_5 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260608_3 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2); 20260528_3 (Cơ sở 2); 20260531_2 (Cơ sở 1); 20260602_3 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260604_3 (Cơ sở 2); 20260608_2 (Cơ sở 1); 20260609_3 (Cơ sở 2); 20260612_4 (Cơ sở 1); 20260613_2 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -6050,11 +6206,11 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>20260601_5 (Cơ sở 1); 20260602_5 (Cơ sở 1); 20260603_1 (Cơ sở 2); 20260608_4 (Cơ sở 1); 20260611_1 (Cơ sở 1)</t>
+          <t>20260519_5 (Cơ sở 1); 20260527_5 (Cơ sở 1); 20260528_5 (Cơ sở 1); 20260531_2 (Cơ sở 1); 20260601_3 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260608_4 (Cơ sở 1); 20260612_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6084,11 +6240,11 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>20260526_5 (Cơ sở 1); 20260601_2 (Cơ sở 2); 20260608_3 (Cơ sở 1); 20260613_3 (Cơ sở 1); 20260608_1 (Cơ sở 2); 20260612_4 (Cơ sở 2)</t>
+          <t>20260602_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260604_1 (Cơ sở 2); 20260608_2 (Cơ sở 1); 20260611_3 (Cơ sở 1); 20260612_3 (Cơ sở 1); 20260612_4 (Cơ sở 1); 20260613_3 (Cơ sở 2); 20260613_4 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -6118,11 +6274,11 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2); 20260527_2 (Cơ sở 2); 20260528_3 (Cơ sở 2); 20260601_4 (Cơ sở 2); 20260608_3 (Cơ sở 1)</t>
+          <t>20260528_3 (Cơ sở 1); 20260530_3 (Cơ sở 1); 20260602_2 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260608_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260612_3 (Cơ sở 1); 20260612_4 (Cơ sở 1); 20260610_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6152,11 +6308,11 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>20260523_3 (Cơ sở 1); 20260525_5 (Cơ sở 1); 20260528_1 (Cơ sở 1); 20260530_3 (Cơ sở 1); 20260603_1 (Cơ sở 2); 20260609_2 (Cơ sở 2)</t>
+          <t>20260602_1 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260605_3 (Cơ sở 1); 20260610_3 (Cơ sở 1); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 1); 20260613_3 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6186,11 +6342,11 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>20260531_2 (Cơ sở 1); 20260601_4 (Cơ sở 2); 20260604_2 (Cơ sở 1); 20260605_3 (Cơ sở 1); 20260613_3 (Cơ sở 1)</t>
+          <t>20260525_2 (Cơ sở 2); 20260528_3 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260608_3 (Cơ sở 1); 20260610_3 (Cơ sở 1); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6220,11 +6376,11 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>20260530_2 (Cơ sở 1); 20260603_3 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260613_3 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260609_3 (Cơ sở 2); 20260613_3 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -6254,11 +6410,11 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>20260519_5 (Cơ sở 1); 20260602_1 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260613_3 (Cơ sở 2); 20260610_4 (Cơ sở 1)</t>
+          <t>20260601_2 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260605_3 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_3 (Cơ sở 1); 20260612_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6288,11 +6444,11 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>20260601_5 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260608_3 (Cơ sở 2); 20260610_1 (Cơ sở 2); 20260612_4 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2); 20260529_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260612_1 (Cơ sở 1); 20260612_2 (Cơ sở 1); 20260612_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6322,11 +6478,11 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>20260529_3 (Cơ sở 1); 20260604_2 (Cơ sở 2); 20260611_3 (Cơ sở 1); 20260612_4 (Cơ sở 1); 20260613_3 (Cơ sở 2); 20260611_1 (Cơ sở 1)</t>
+          <t>20260529_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260609_3 (Cơ sở 2); 20260612_2 (Cơ sở 1); 20260613_4 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -6356,11 +6512,11 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>20260519_5 (Cơ sở 1); 20260528_4 (Cơ sở 1); 20260601_5 (Cơ sở 1); 20260605_3 (Cơ sở 1); 20260613_3 (Cơ sở 2)</t>
+          <t>20260528_2 (Cơ sở 1); 20260529_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260604_2 (Cơ sở 1); 20260605_3 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260612_4 (Cơ sở 1); 20260613_3 (Cơ sở 1); 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6390,11 +6546,11 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 1); 20260602_5 (Cơ sở 1); 20260605_3 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260610_3 (Cơ sở 1)</t>
+          <t>20260528_4 (Cơ sở 1); 20260529_1 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260609_3 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260613_3 (Cơ sở 2); 20260613_4 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -6424,11 +6580,11 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260609_3 (Cơ sở 2); 20260608_2 (Cơ sở 2); 20260611_1 (Cơ sở 1)</t>
+          <t>20260523_3 (Cơ sở 1); 20260526_5 (Cơ sở 1); 20260601_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260604_2 (Cơ sở 1); 20260605_3 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260609_2 (Cơ sở 1); 20260611_3 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -6458,11 +6614,11 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>20260523_3 (Cơ sở 1); 20260525_2 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260613_3 (Cơ sở 1); 20260610_1 (Cơ sở 1)</t>
+          <t>20260601_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260604_1 (Cơ sở 2); 20260604_2 (Cơ sở 2); 20260608_3 (Cơ sở 1); 20260608_4 (Cơ sở 1); 20260609_2 (Cơ sở 2); 20260612_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6492,11 +6648,11 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1); 20260528_3 (Cơ sở 2); 20260529_2 (Cơ sở 1); 20260610_3 (Cơ sở 1); 20260613_2 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2); 20260530_3 (Cơ sở 1); 20260602_2 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260612_1 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6526,11 +6682,11 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2); 20260529_2 (Cơ sở 1); 20260603_2 (Cơ sở 2); 20260608_2 (Cơ sở 1); 20260613_1 (Cơ sở 1)</t>
+          <t>20260523_3 (Cơ sở 1); 20260525_2 (Cơ sở 2); 20260529_1 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260605_3 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260612_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6560,11 +6716,11 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>20260529_2 (Cơ sở 1); 20260530_3 (Cơ sở 1); 20260601_5 (Cơ sở 1); 20260604_2 (Cơ sở 1); 20260605_4 (Cơ sở 1)</t>
+          <t>20260529_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260601_3 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_4 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_2 (Cơ sở 1); 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6594,11 +6750,11 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>20260528_1 (Cơ sở 1); 20260601_4 (Cơ sở 2); 20260602_5 (Cơ sở 1); 20260604_2 (Cơ sở 2); 20260613_4 (Cơ sở 2)</t>
+          <t>20260518_5 (Cơ sở 1); 20260529_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260605_2 (Cơ sở 1); 20260611_3 (Cơ sở 2); 20260608_4 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -6628,11 +6784,11 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>20260602_4 (Cơ sở 2); 20260605_4 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260611_3 (Cơ sở 1); 20260612_3 (Cơ sở 1)</t>
+          <t>20260529_1 (Cơ sở 2); 20260601_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260612_2 (Cơ sở 1); 20260612_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6662,11 +6818,11 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1); 20260529_1 (Cơ sở 1); 20260530_2 (Cơ sở 1); 20260605_2 (Cơ sở 1); 20260608_4 (Cơ sở 2)</t>
+          <t>20260602_2 (Cơ sở 2); 20260603_1 (Cơ sở 2); 20260603_3 (Cơ sở 2); 20260605_3 (Cơ sở 1); 20260608_3 (Cơ sở 1); 20260610_3 (Cơ sở 2); 20260611_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260612_4 (Cơ sở 1); 20260613_1 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6696,11 +6852,11 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>20260528_5 (Cơ sở 1); 20260529_1 (Cơ sở 2); 20260530_3 (Cơ sở 1); 20260605_2 (Cơ sở 1); 20260608_3 (Cơ sở 1)</t>
+          <t>20260527_4 (Cơ sở 1); 20260529_1 (Cơ sở 2); 20260602_2 (Cơ sở 2); 20260602_3 (Cơ sở 2); 20260603_2 (Cơ sở 2); 20260603_4 (Cơ sở 2); 20260609_3 (Cơ sở 2); 20260610_3 (Cơ sở 2); 20260612_1 (Cơ sở 1); 20260613_4 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6913,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>387</v>
+        <v>769</v>
       </c>
     </row>
     <row r="5">
@@ -6767,7 +6923,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3014</v>
+        <v>10.5342</v>
       </c>
     </row>
     <row r="6">
@@ -6777,7 +6933,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -6787,7 +6943,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -6807,7 +6963,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4589</v>
+        <v>0.4988</v>
       </c>
     </row>
   </sheetData>
